--- a/backend/data/attachments/risk_风险限额使用情况_7.xlsx
+++ b/backend/data/attachments/risk_风险限额使用情况_7.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trust-456</t>
+          <t>Trust-688</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31761</v>
+        <v>24390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -464,12 +464,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,11 +481,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trust-437</t>
+          <t>Trust-108</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31977</v>
+        <v>42088</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -494,12 +494,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -511,41 +511,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trust-565</t>
+          <t>Trust-721</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10771</v>
+        <v>28089</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trust-985</t>
+          <t>Trust-743</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38724</v>
+        <v>11367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -554,12 +554,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -571,11 +571,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trust-630</t>
+          <t>Trust-849</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28709</v>
+        <v>13612</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -584,42 +584,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trust-662</t>
+          <t>Trust-279</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13586</v>
+        <v>18159</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -631,25 +631,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trust-129</t>
+          <t>Trust-950</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46289</v>
+        <v>15783</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -661,11 +661,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trust-665</t>
+          <t>Trust-923</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31738</v>
+        <v>12547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -674,12 +674,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
